--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run8/epoch_120/per_file_predictions_epoch_120.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run8/epoch_120/per_file_predictions_epoch_120.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="522">
   <si>
     <t>Filename</t>
   </si>
@@ -808,772 +808,778 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0,1,0,1</t>
-  </si>
-  <si>
-    <t>0.5252,0.3222,0.0062,0.1039</t>
-  </si>
-  <si>
-    <t>0.0296,0.0030,0.0021,0.9874</t>
-  </si>
-  <si>
-    <t>0.5703,0.0071,0.0023,0.6042</t>
-  </si>
-  <si>
-    <t>0.2170,0.0059,0.0034,0.9081</t>
-  </si>
-  <si>
-    <t>0.9975,0.0008,0.0001,0.0005</t>
-  </si>
-  <si>
-    <t>0.9942,0.0020,0.0001,0.0012</t>
-  </si>
-  <si>
-    <t>0.9897,0.0071,0.0006,0.0011</t>
-  </si>
-  <si>
-    <t>0.9950,0.0018,0.0002,0.0014</t>
-  </si>
-  <si>
-    <t>0.9979,0.0014,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9912,0.0074,0.0003,0.0007</t>
-  </si>
-  <si>
-    <t>0.9953,0.0034,0.0007,0.0003</t>
-  </si>
-  <si>
-    <t>0.9985,0.0002,0.0000,0.0004</t>
-  </si>
-  <si>
-    <t>0.3993,0.2974,0.3712,0.0165</t>
-  </si>
-  <si>
-    <t>0.3977,0.1325,0.5296,0.0079</t>
-  </si>
-  <si>
-    <t>0.1325,0.0230,0.9185,0.0034</t>
-  </si>
-  <si>
-    <t>0.3295,0.0257,0.7714,0.0084</t>
-  </si>
-  <si>
-    <t>0.5641,0.0794,0.4500,0.0081</t>
-  </si>
-  <si>
-    <t>0.0118,0.9771,0.0114,0.0018</t>
-  </si>
-  <si>
-    <t>0.0120,0.9794,0.0039,0.0014</t>
-  </si>
-  <si>
-    <t>0.0353,0.9623,0.0015,0.0017</t>
-  </si>
-  <si>
-    <t>0.0271,0.9709,0.0013,0.0004</t>
-  </si>
-  <si>
-    <t>0.0009,0.9964,0.0024,0.0002</t>
-  </si>
-  <si>
-    <t>0.5848,0.0039,0.2922,0.0535</t>
-  </si>
-  <si>
-    <t>0.3548,0.0392,0.6798,0.0242</t>
-  </si>
-  <si>
-    <t>0.0818,0.0084,0.9261,0.0175</t>
-  </si>
-  <si>
-    <t>0.0432,0.0156,0.9306,0.0262</t>
-  </si>
-  <si>
-    <t>0.1057,0.0050,0.9503,0.0036</t>
-  </si>
-  <si>
-    <t>0.0723,0.0022,0.9685,0.0035</t>
-  </si>
-  <si>
-    <t>0.0005,0.0002,0.9981,0.0041</t>
-  </si>
-  <si>
-    <t>0.2463,0.8052,0.0155,0.0018</t>
-  </si>
-  <si>
-    <t>0.6053,0.2228,0.2281,0.0065</t>
-  </si>
-  <si>
-    <t>0.0010,0.0071,0.9955,0.0055</t>
-  </si>
-  <si>
-    <t>0.0240,0.6407,0.6615,0.0002</t>
-  </si>
-  <si>
-    <t>0.8940,0.0479,0.0666,0.0072</t>
-  </si>
-  <si>
-    <t>0.8753,0.0704,0.0357,0.0174</t>
-  </si>
-  <si>
-    <t>0.5790,0.5647,0.0160,0.0041</t>
-  </si>
-  <si>
-    <t>0.1328,0.8435,0.1319,0.0028</t>
-  </si>
-  <si>
-    <t>0.0199,0.1886,0.9079,0.0084</t>
-  </si>
-  <si>
-    <t>0.0153,0.0450,0.9612,0.0047</t>
-  </si>
-  <si>
-    <t>0.0332,0.0340,0.9458,0.0032</t>
-  </si>
-  <si>
-    <t>0.4065,0.0264,0.6225,0.0389</t>
-  </si>
-  <si>
-    <t>0.0067,0.0961,0.9743,0.0002</t>
-  </si>
-  <si>
-    <t>0.0139,0.9206,0.1461,0.0180</t>
-  </si>
-  <si>
-    <t>0.0445,0.0723,0.9225,0.0043</t>
-  </si>
-  <si>
-    <t>0.0144,0.7223,0.0131,0.8298</t>
-  </si>
-  <si>
-    <t>0.0009,0.9815,0.0039,0.0883</t>
-  </si>
-  <si>
-    <t>0.0005,0.9939,0.0306,0.0028</t>
-  </si>
-  <si>
-    <t>0.0001,0.9970,0.0288,0.0013</t>
-  </si>
-  <si>
-    <t>0.0005,0.1694,0.9904,0.0010</t>
-  </si>
-  <si>
-    <t>0.0019,0.2176,0.9911,0.0002</t>
-  </si>
-  <si>
-    <t>0.0321,0.0062,0.9595,0.0196</t>
-  </si>
-  <si>
-    <t>0.0095,0.0016,0.9934,0.0010</t>
-  </si>
-  <si>
-    <t>0.0003,0.0034,0.9983,0.0013</t>
-  </si>
-  <si>
-    <t>0.0047,0.0035,0.9934,0.0003</t>
-  </si>
-  <si>
-    <t>0.9681,0.0375,0.0037,0.0012</t>
-  </si>
-  <si>
-    <t>0.9903,0.0106,0.0003,0.0007</t>
-  </si>
-  <si>
-    <t>0.9711,0.0236,0.0080,0.0017</t>
-  </si>
-  <si>
-    <t>0.0126,0.0337,0.9824,0.0021</t>
-  </si>
-  <si>
-    <t>0.9880,0.0058,0.0010,0.0019</t>
-  </si>
-  <si>
-    <t>0.9948,0.0052,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.9783,0.0392,0.0021,0.0003</t>
-  </si>
-  <si>
-    <t>0.0013,0.8570,0.9196,0.0003</t>
-  </si>
-  <si>
-    <t>0.0046,0.0437,0.9900,0.0004</t>
-  </si>
-  <si>
-    <t>0.0060,0.0396,0.9842,0.0006</t>
-  </si>
-  <si>
-    <t>0.0027,0.6192,0.9461,0.0005</t>
-  </si>
-  <si>
-    <t>0.0094,0.0077,0.9848,0.0049</t>
-  </si>
-  <si>
-    <t>0.0243,0.8220,0.1743,0.0001</t>
-  </si>
-  <si>
-    <t>0.0111,0.9837,0.0029,0.0005</t>
-  </si>
-  <si>
-    <t>0.9515,0.0458,0.0074,0.0016</t>
-  </si>
-  <si>
-    <t>0.5915,0.2411,0.2200,0.0027</t>
-  </si>
-  <si>
-    <t>0.0035,0.0208,0.9881,0.0056</t>
-  </si>
-  <si>
-    <t>0.0012,0.8005,0.8944,0.0000</t>
-  </si>
-  <si>
-    <t>0.0012,0.7403,0.9454,0.0001</t>
-  </si>
-  <si>
-    <t>0.0048,0.9660,0.2746,0.0014</t>
-  </si>
-  <si>
-    <t>0.0006,0.8942,0.9240,0.0001</t>
-  </si>
-  <si>
-    <t>0.0480,0.0005,0.0370,0.9389</t>
-  </si>
-  <si>
-    <t>0.0080,0.0104,0.0007,0.9943</t>
-  </si>
-  <si>
-    <t>0.0078,0.0004,0.0020,0.9947</t>
-  </si>
-  <si>
-    <t>0.2381,0.0012,0.0025,0.9158</t>
-  </si>
-  <si>
-    <t>0.0081,0.0096,0.0045,0.9934</t>
-  </si>
-  <si>
-    <t>0.0150,0.0021,0.0042,0.9910</t>
-  </si>
-  <si>
-    <t>0.0024,0.8486,0.8427,0.0002</t>
-  </si>
-  <si>
-    <t>0.0008,0.6699,0.9872,0.0001</t>
-  </si>
-  <si>
-    <t>0.0073,0.8535,0.5943,0.0015</t>
-  </si>
-  <si>
-    <t>0.0084,0.5543,0.8885,0.0009</t>
-  </si>
-  <si>
-    <t>0.0002,0.9648,0.9407,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.2112,0.9894,0.0001</t>
-  </si>
-  <si>
-    <t>0.9909,0.0082,0.0004,0.0007</t>
-  </si>
-  <si>
-    <t>0.9974,0.0012,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9873,0.0170,0.0005,0.0004</t>
-  </si>
-  <si>
-    <t>0.9932,0.0020,0.0005,0.0013</t>
-  </si>
-  <si>
-    <t>0.9948,0.0029,0.0004,0.0005</t>
-  </si>
-  <si>
-    <t>0.9798,0.0132,0.0033,0.0021</t>
-  </si>
-  <si>
-    <t>0.9906,0.0105,0.0015,0.0004</t>
-  </si>
-  <si>
-    <t>0.9941,0.0028,0.0005,0.0006</t>
-  </si>
-  <si>
-    <t>0.9988,0.0003,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9951,0.0033,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9949,0.0035,0.0004,0.0004</t>
-  </si>
-  <si>
-    <t>0.9939,0.0022,0.0007,0.0011</t>
-  </si>
-  <si>
-    <t>0.9121,0.1766,0.0037,0.0003</t>
-  </si>
-  <si>
-    <t>0.9886,0.0067,0.0009,0.0016</t>
-  </si>
-  <si>
-    <t>0.9882,0.0147,0.0009,0.0004</t>
-  </si>
-  <si>
-    <t>0.9919,0.0060,0.0013,0.0005</t>
-  </si>
-  <si>
-    <t>0.0004,0.0021,0.9967,0.0051</t>
-  </si>
-  <si>
-    <t>0.0511,0.0228,0.9419,0.0021</t>
-  </si>
-  <si>
-    <t>0.3699,0.1255,0.1107,0.5353</t>
-  </si>
-  <si>
-    <t>0.0251,0.0077,0.9728,0.0041</t>
-  </si>
-  <si>
-    <t>0.0068,0.9879,0.0025,0.0006</t>
-  </si>
-  <si>
-    <t>0.0119,0.9758,0.0093,0.0013</t>
-  </si>
-  <si>
-    <t>0.0121,0.9767,0.0004,0.0037</t>
-  </si>
-  <si>
-    <t>0.6307,0.5261,0.0056,0.0016</t>
-  </si>
-  <si>
-    <t>0.0257,0.9675,0.0015,0.0012</t>
-  </si>
-  <si>
-    <t>0.0071,0.9864,0.0013,0.0004</t>
-  </si>
-  <si>
-    <t>0.4592,0.7431,0.0022,0.0004</t>
-  </si>
-  <si>
-    <t>0.6751,0.1910,0.2074,0.0065</t>
-  </si>
-  <si>
-    <t>0.1438,0.0058,0.8800,0.0590</t>
-  </si>
-  <si>
-    <t>0.4423,0.0681,0.5692,0.0139</t>
-  </si>
-  <si>
-    <t>0.6893,0.0557,0.1926,0.0503</t>
-  </si>
-  <si>
-    <t>0.1957,0.1126,0.0493,0.7847</t>
-  </si>
-  <si>
-    <t>0.0009,0.9953,0.0384,0.0003</t>
-  </si>
-  <si>
-    <t>0.0013,0.9910,0.0208,0.0037</t>
-  </si>
-  <si>
-    <t>0.0244,0.9102,0.0171,0.1249</t>
-  </si>
-  <si>
-    <t>0.0002,0.9790,0.7075,0.0003</t>
-  </si>
-  <si>
-    <t>0.0210,0.9701,0.0315,0.0007</t>
-  </si>
-  <si>
-    <t>0.8025,0.1715,0.0715,0.0018</t>
-  </si>
-  <si>
-    <t>0.8429,0.2513,0.0128,0.0007</t>
-  </si>
-  <si>
-    <t>0.9960,0.0011,0.0002,0.0010</t>
-  </si>
-  <si>
-    <t>0.9778,0.0059,0.0064,0.0044</t>
-  </si>
-  <si>
-    <t>0.9882,0.0043,0.0004,0.0025</t>
-  </si>
-  <si>
-    <t>0.9911,0.0050,0.0003,0.0012</t>
-  </si>
-  <si>
-    <t>0.9953,0.0006,0.0001,0.0025</t>
-  </si>
-  <si>
-    <t>0.9750,0.0151,0.0142,0.0010</t>
-  </si>
-  <si>
-    <t>0.9868,0.0099,0.0005,0.0014</t>
-  </si>
-  <si>
-    <t>0.9815,0.0140,0.0038,0.0012</t>
-  </si>
-  <si>
-    <t>0.0005,0.0260,0.9971,0.0003</t>
-  </si>
-  <si>
-    <t>0.0133,0.3843,0.8509,0.0008</t>
-  </si>
-  <si>
-    <t>0.0183,0.0548,0.9385,0.0116</t>
-  </si>
-  <si>
-    <t>0.0062,0.0057,0.9923,0.0003</t>
-  </si>
-  <si>
-    <t>0.8568,0.0096,0.0667,0.0202</t>
-  </si>
-  <si>
-    <t>0.6361,0.1076,0.3454,0.0143</t>
-  </si>
-  <si>
-    <t>0.2563,0.0291,0.8353,0.0071</t>
-  </si>
-  <si>
-    <t>0.3657,0.2731,0.4727,0.0181</t>
-  </si>
-  <si>
-    <t>0.0583,0.0009,0.0025,0.9774</t>
-  </si>
-  <si>
-    <t>0.0004,0.0006,0.0024,0.9987</t>
-  </si>
-  <si>
-    <t>0.0144,0.0133,0.0019,0.9907</t>
-  </si>
-  <si>
-    <t>0.0230,0.0005,0.0007,0.9935</t>
-  </si>
-  <si>
-    <t>0.0019,0.7883,0.8983,0.0016</t>
-  </si>
-  <si>
-    <t>0.9861,0.0070,0.0009,0.0024</t>
-  </si>
-  <si>
-    <t>0.0206,0.9747,0.0034,0.0017</t>
-  </si>
-  <si>
-    <t>0.9889,0.0022,0.0004,0.0042</t>
-  </si>
-  <si>
-    <t>0.8824,0.2161,0.0093,0.0008</t>
-  </si>
-  <si>
-    <t>0.9670,0.0030,0.0075,0.0091</t>
-  </si>
-  <si>
-    <t>0.7484,0.1002,0.1075,0.0964</t>
-  </si>
-  <si>
-    <t>0.9800,0.0070,0.0037,0.0041</t>
-  </si>
-  <si>
-    <t>0.0000,0.0385,0.9977,0.0008</t>
-  </si>
-  <si>
-    <t>0.7985,0.0124,0.2258,0.0114</t>
-  </si>
-  <si>
-    <t>0.9442,0.0172,0.0307,0.0055</t>
-  </si>
-  <si>
-    <t>0.2610,0.7299,0.0549,0.0066</t>
-  </si>
-  <si>
-    <t>0.8995,0.1002,0.0014,0.0047</t>
-  </si>
-  <si>
-    <t>0.9509,0.0373,0.0120,0.0022</t>
-  </si>
-  <si>
-    <t>0.7287,0.1374,0.0998,0.0402</t>
-  </si>
-  <si>
-    <t>0.7576,0.1956,0.0638,0.0052</t>
-  </si>
-  <si>
-    <t>0.9201,0.0329,0.0208,0.0055</t>
-  </si>
-  <si>
-    <t>0.9937,0.0008,0.0002,0.0030</t>
-  </si>
-  <si>
-    <t>0.9910,0.0051,0.0005,0.0012</t>
-  </si>
-  <si>
-    <t>0.9906,0.0018,0.0010,0.0030</t>
-  </si>
-  <si>
-    <t>0.9917,0.0019,0.0021,0.0015</t>
-  </si>
-  <si>
-    <t>0.9866,0.0058,0.0012,0.0026</t>
-  </si>
-  <si>
-    <t>0.9889,0.0059,0.0013,0.0011</t>
-  </si>
-  <si>
-    <t>0.9921,0.0016,0.0006,0.0026</t>
-  </si>
-  <si>
-    <t>0.9826,0.0088,0.0025,0.0020</t>
-  </si>
-  <si>
-    <t>0.4441,0.5913,0.0603,0.0012</t>
-  </si>
-  <si>
-    <t>0.4899,0.6528,0.0110,0.0015</t>
-  </si>
-  <si>
-    <t>0.3379,0.7145,0.0394,0.0024</t>
-  </si>
-  <si>
-    <t>0.0532,0.6151,0.7013,0.0005</t>
-  </si>
-  <si>
-    <t>0.9887,0.0059,0.0021,0.0008</t>
-  </si>
-  <si>
-    <t>0.9436,0.0416,0.0239,0.0011</t>
-  </si>
-  <si>
-    <t>0.9850,0.0042,0.0016,0.0034</t>
-  </si>
-  <si>
-    <t>0.9723,0.0370,0.0053,0.0002</t>
-  </si>
-  <si>
-    <t>0.0007,0.0063,0.9985,0.0002</t>
-  </si>
-  <si>
-    <t>0.9698,0.0249,0.0100,0.0008</t>
-  </si>
-  <si>
-    <t>0.0032,0.0055,0.9948,0.0007</t>
-  </si>
-  <si>
-    <t>0.0078,0.0197,0.9846,0.0040</t>
-  </si>
-  <si>
-    <t>0.0840,0.0062,0.9476,0.0069</t>
-  </si>
-  <si>
-    <t>0.0003,0.0204,0.9967,0.0006</t>
-  </si>
-  <si>
-    <t>0.0386,0.0939,0.9338,0.0044</t>
-  </si>
-  <si>
-    <t>0.0139,0.0080,0.9822,0.0013</t>
-  </si>
-  <si>
-    <t>0.0016,0.0073,0.9937,0.0015</t>
-  </si>
-  <si>
-    <t>0.1829,0.4925,0.3058,0.0041</t>
-  </si>
-  <si>
-    <t>0.0654,0.0080,0.9696,0.0017</t>
-  </si>
-  <si>
-    <t>0.4278,0.2911,0.3825,0.0385</t>
-  </si>
-  <si>
-    <t>0.5197,0.1551,0.3893,0.0149</t>
-  </si>
-  <si>
-    <t>0.1087,0.5232,0.4244,0.0023</t>
-  </si>
-  <si>
-    <t>0.6400,0.1678,0.2211,0.0043</t>
-  </si>
-  <si>
-    <t>0.5058,0.0318,0.6012,0.0224</t>
-  </si>
-  <si>
-    <t>0.2636,0.0273,0.8080,0.0053</t>
-  </si>
-  <si>
-    <t>0.8278,0.3311,0.0070,0.0009</t>
-  </si>
-  <si>
-    <t>0.4039,0.7602,0.0045,0.0004</t>
-  </si>
-  <si>
-    <t>0.7458,0.4413,0.0053,0.0009</t>
-  </si>
-  <si>
-    <t>0.9861,0.0232,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.9610,0.0789,0.0022,0.0006</t>
-  </si>
-  <si>
-    <t>0.5600,0.0403,0.4170,0.0396</t>
-  </si>
-  <si>
-    <t>0.7630,0.0288,0.3043,0.0072</t>
-  </si>
-  <si>
-    <t>0.5597,0.0271,0.1957,0.1700</t>
-  </si>
-  <si>
-    <t>0.6052,0.0202,0.4582,0.0241</t>
-  </si>
-  <si>
-    <t>0.4052,0.0102,0.6903,0.0295</t>
-  </si>
-  <si>
-    <t>0.0156,0.0103,0.9730,0.0117</t>
-  </si>
-  <si>
-    <t>0.0227,0.0264,0.9599,0.0015</t>
-  </si>
-  <si>
-    <t>0.0405,0.0578,0.9207,0.0060</t>
-  </si>
-  <si>
-    <t>0.0967,0.0256,0.8873,0.0042</t>
-  </si>
-  <si>
-    <t>0.0130,0.0669,0.9628,0.0008</t>
-  </si>
-  <si>
-    <t>0.9926,0.0075,0.0004,0.0005</t>
-  </si>
-  <si>
-    <t>0.9743,0.0319,0.0037,0.0006</t>
-  </si>
-  <si>
-    <t>0.9835,0.0131,0.0022,0.0013</t>
-  </si>
-  <si>
-    <t>0.9686,0.0547,0.0017,0.0008</t>
-  </si>
-  <si>
-    <t>0.9957,0.0024,0.0002,0.0005</t>
-  </si>
-  <si>
-    <t>0.9887,0.0123,0.0004,0.0005</t>
-  </si>
-  <si>
-    <t>0.9951,0.0044,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9667,0.0440,0.0069,0.0006</t>
-  </si>
-  <si>
-    <t>0.0438,0.0314,0.9621,0.0015</t>
-  </si>
-  <si>
-    <t>0.3327,0.5755,0.1990,0.0072</t>
-  </si>
-  <si>
-    <t>0.6952,0.0246,0.1775,0.0782</t>
-  </si>
-  <si>
-    <t>0.0016,0.0143,0.9948,0.0008</t>
-  </si>
-  <si>
-    <t>0.0008,0.1077,0.9893,0.0018</t>
-  </si>
-  <si>
-    <t>0.0160,0.0813,0.9448,0.0017</t>
-  </si>
-  <si>
-    <t>0.0028,0.0067,0.9952,0.0007</t>
-  </si>
-  <si>
-    <t>0.0827,0.0589,0.8581,0.0025</t>
-  </si>
-  <si>
-    <t>0.0063,0.0094,0.9906,0.0013</t>
-  </si>
-  <si>
-    <t>0.0019,0.0219,0.9916,0.0007</t>
-  </si>
-  <si>
-    <t>0.1062,0.0610,0.8490,0.0076</t>
-  </si>
-  <si>
-    <t>0.0830,0.0029,0.9564,0.0065</t>
-  </si>
-  <si>
-    <t>0.1740,0.0029,0.5867,0.2834</t>
-  </si>
-  <si>
-    <t>0.5234,0.0152,0.2301,0.1837</t>
-  </si>
-  <si>
-    <t>0.9851,0.0241,0.0023,0.0001</t>
-  </si>
-  <si>
-    <t>0.9926,0.0032,0.0002,0.0016</t>
-  </si>
-  <si>
-    <t>0.9966,0.0007,0.0001,0.0011</t>
-  </si>
-  <si>
-    <t>0.9954,0.0053,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9887,0.0023,0.0010,0.0042</t>
-  </si>
-  <si>
-    <t>0.9935,0.0036,0.0002,0.0009</t>
-  </si>
-  <si>
-    <t>0.9934,0.0038,0.0007,0.0006</t>
-  </si>
-  <si>
-    <t>0.9927,0.0086,0.0007,0.0002</t>
-  </si>
-  <si>
-    <t>0.0142,0.1257,0.9433,0.0017</t>
-  </si>
-  <si>
-    <t>0.0014,0.0147,0.9956,0.0005</t>
-  </si>
-  <si>
-    <t>0.0018,0.0092,0.9936,0.0008</t>
-  </si>
-  <si>
-    <t>0.0537,0.0213,0.9154,0.0201</t>
-  </si>
-  <si>
-    <t>0.0047,0.0045,0.9932,0.0010</t>
-  </si>
-  <si>
-    <t>0.1212,0.0043,0.8083,0.0733</t>
-  </si>
-  <si>
-    <t>0.0440,0.0567,0.9276,0.0035</t>
-  </si>
-  <si>
-    <t>0.0267,0.0059,0.9304,0.0643</t>
-  </si>
-  <si>
-    <t>0.3973,0.0069,0.0502,0.6327</t>
-  </si>
-  <si>
-    <t>0.0656,0.0961,0.0001,0.8529</t>
-  </si>
-  <si>
-    <t>0.0242,0.0013,0.0003,0.9929</t>
-  </si>
-  <si>
-    <t>0.0021,0.0016,0.0080,0.9960</t>
-  </si>
-  <si>
-    <t>0.0067,0.0001,0.0002,0.9980</t>
-  </si>
-  <si>
-    <t>0.4660,0.0856,0.0168,0.4052</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0.5166,0.3429,0.1783,0.0473</t>
+  </si>
+  <si>
+    <t>0.0074,0.0011,0.0106,0.9905</t>
+  </si>
+  <si>
+    <t>0.8093,0.0127,0.0103,0.1916</t>
+  </si>
+  <si>
+    <t>0.0609,0.0037,0.0060,0.9730</t>
+  </si>
+  <si>
+    <t>0.9967,0.0020,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9895,0.0168,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9923,0.0058,0.0003,0.0007</t>
+  </si>
+  <si>
+    <t>0.9981,0.0006,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9850,0.0252,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.9874,0.0230,0.0006,0.0003</t>
+  </si>
+  <si>
+    <t>0.9915,0.0030,0.0005,0.0016</t>
+  </si>
+  <si>
+    <t>0.9982,0.0007,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.6209,0.0431,0.3998,0.0253</t>
+  </si>
+  <si>
+    <t>0.2611,0.0225,0.8473,0.0088</t>
+  </si>
+  <si>
+    <t>0.0408,0.0318,0.9615,0.0007</t>
+  </si>
+  <si>
+    <t>0.0310,0.0380,0.9386,0.0011</t>
+  </si>
+  <si>
+    <t>0.6354,0.0430,0.3977,0.0130</t>
+  </si>
+  <si>
+    <t>0.0057,0.9890,0.0081,0.0006</t>
+  </si>
+  <si>
+    <t>0.0339,0.9594,0.0104,0.0018</t>
+  </si>
+  <si>
+    <t>0.0795,0.9352,0.0006,0.0018</t>
+  </si>
+  <si>
+    <t>0.0746,0.9333,0.0103,0.0007</t>
+  </si>
+  <si>
+    <t>0.0023,0.9942,0.0020,0.0001</t>
+  </si>
+  <si>
+    <t>0.0535,0.0052,0.8937,0.1317</t>
+  </si>
+  <si>
+    <t>0.1703,0.0038,0.8979,0.0070</t>
+  </si>
+  <si>
+    <t>0.0229,0.0122,0.9612,0.0129</t>
+  </si>
+  <si>
+    <t>0.1037,0.0363,0.8541,0.0128</t>
+  </si>
+  <si>
+    <t>0.0640,0.0083,0.9564,0.0063</t>
+  </si>
+  <si>
+    <t>0.2658,0.0250,0.8009,0.0042</t>
+  </si>
+  <si>
+    <t>0.0015,0.0011,0.9965,0.0026</t>
+  </si>
+  <si>
+    <t>0.3878,0.7328,0.0117,0.0018</t>
+  </si>
+  <si>
+    <t>0.7902,0.1391,0.1379,0.0035</t>
+  </si>
+  <si>
+    <t>0.0012,0.0136,0.9944,0.0038</t>
+  </si>
+  <si>
+    <t>0.0240,0.9239,0.1009,0.0006</t>
+  </si>
+  <si>
+    <t>0.8997,0.0342,0.0218,0.0258</t>
+  </si>
+  <si>
+    <t>0.9031,0.0802,0.0316,0.0025</t>
+  </si>
+  <si>
+    <t>0.9349,0.0914,0.0040,0.0016</t>
+  </si>
+  <si>
+    <t>0.0254,0.9518,0.2060,0.0012</t>
+  </si>
+  <si>
+    <t>0.0107,0.2253,0.9032,0.0147</t>
+  </si>
+  <si>
+    <t>0.1380,0.0423,0.7809,0.0545</t>
+  </si>
+  <si>
+    <t>0.0547,0.0500,0.8460,0.0697</t>
+  </si>
+  <si>
+    <t>0.0215,0.0471,0.9276,0.0347</t>
+  </si>
+  <si>
+    <t>0.0310,0.0853,0.9261,0.0015</t>
+  </si>
+  <si>
+    <t>0.0277,0.7908,0.2687,0.0428</t>
+  </si>
+  <si>
+    <t>0.0179,0.0182,0.9644,0.0092</t>
+  </si>
+  <si>
+    <t>0.0279,0.9189,0.0272,0.1072</t>
+  </si>
+  <si>
+    <t>0.0052,0.9734,0.0218,0.0181</t>
+  </si>
+  <si>
+    <t>0.0007,0.9881,0.1042,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.9990,0.0042,0.0004</t>
+  </si>
+  <si>
+    <t>0.0008,0.0119,0.9936,0.0042</t>
+  </si>
+  <si>
+    <t>0.0066,0.0878,0.9834,0.0006</t>
+  </si>
+  <si>
+    <t>0.0057,0.0100,0.9831,0.0076</t>
+  </si>
+  <si>
+    <t>0.0258,0.0020,0.9833,0.0027</t>
+  </si>
+  <si>
+    <t>0.0002,0.0020,0.9983,0.0023</t>
+  </si>
+  <si>
+    <t>0.0143,0.0326,0.9638,0.0011</t>
+  </si>
+  <si>
+    <t>0.9804,0.0257,0.0024,0.0004</t>
+  </si>
+  <si>
+    <t>0.9793,0.0163,0.0028,0.0014</t>
+  </si>
+  <si>
+    <t>0.9603,0.0079,0.0322,0.0043</t>
+  </si>
+  <si>
+    <t>0.0035,0.0377,0.9918,0.0037</t>
+  </si>
+  <si>
+    <t>0.9932,0.0026,0.0002,0.0012</t>
+  </si>
+  <si>
+    <t>0.9963,0.0017,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9646,0.0518,0.0037,0.0010</t>
+  </si>
+  <si>
+    <t>0.0010,0.8099,0.9732,0.0003</t>
+  </si>
+  <si>
+    <t>0.0009,0.0080,0.9963,0.0010</t>
+  </si>
+  <si>
+    <t>0.0259,0.0325,0.9587,0.0061</t>
+  </si>
+  <si>
+    <t>0.0006,0.6642,0.9825,0.0001</t>
+  </si>
+  <si>
+    <t>0.0007,0.0090,0.9970,0.0004</t>
+  </si>
+  <si>
+    <t>0.0072,0.9816,0.0291,0.0003</t>
+  </si>
+  <si>
+    <t>0.0151,0.9756,0.0080,0.0005</t>
+  </si>
+  <si>
+    <t>0.9487,0.0378,0.0123,0.0020</t>
+  </si>
+  <si>
+    <t>0.6253,0.2125,0.2535,0.0060</t>
+  </si>
+  <si>
+    <t>0.0328,0.0747,0.9310,0.0123</t>
+  </si>
+  <si>
+    <t>0.0010,0.8843,0.9039,0.0002</t>
+  </si>
+  <si>
+    <t>0.0016,0.7899,0.9021,0.0002</t>
+  </si>
+  <si>
+    <t>0.0018,0.8215,0.9146,0.0005</t>
+  </si>
+  <si>
+    <t>0.0025,0.9623,0.4767,0.0011</t>
+  </si>
+  <si>
+    <t>0.0239,0.0008,0.0997,0.9366</t>
+  </si>
+  <si>
+    <t>0.0043,0.0012,0.0007,0.9976</t>
+  </si>
+  <si>
+    <t>0.0132,0.0021,0.0044,0.9913</t>
+  </si>
+  <si>
+    <t>0.0060,0.0132,0.0050,0.9925</t>
+  </si>
+  <si>
+    <t>0.1060,0.0048,0.0202,0.9404</t>
+  </si>
+  <si>
+    <t>0.0050,0.0042,0.0120,0.9919</t>
+  </si>
+  <si>
+    <t>0.0035,0.7577,0.9402,0.0006</t>
+  </si>
+  <si>
+    <t>0.0017,0.2343,0.9888,0.0002</t>
+  </si>
+  <si>
+    <t>0.0042,0.2209,0.9608,0.0002</t>
+  </si>
+  <si>
+    <t>0.0023,0.6464,0.9458,0.0001</t>
+  </si>
+  <si>
+    <t>0.0008,0.7974,0.9373,0.0001</t>
+  </si>
+  <si>
+    <t>0.0079,0.8339,0.6039,0.0019</t>
+  </si>
+  <si>
+    <t>0.9971,0.0016,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9914,0.0035,0.0006,0.0015</t>
+  </si>
+  <si>
+    <t>0.9934,0.0055,0.0005,0.0004</t>
+  </si>
+  <si>
+    <t>0.9872,0.0147,0.0023,0.0003</t>
+  </si>
+  <si>
+    <t>0.9861,0.0109,0.0012,0.0013</t>
+  </si>
+  <si>
+    <t>0.9912,0.0066,0.0012,0.0005</t>
+  </si>
+  <si>
+    <t>0.9939,0.0044,0.0005,0.0005</t>
+  </si>
+  <si>
+    <t>0.9954,0.0029,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9953,0.0028,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.9983,0.0007,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9970,0.0004,0.0001,0.0015</t>
+  </si>
+  <si>
+    <t>0.9969,0.0013,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9964,0.0016,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.9943,0.0051,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.9953,0.0019,0.0006,0.0004</t>
+  </si>
+  <si>
+    <t>0.9978,0.0008,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.0005,0.0021,0.9971,0.0038</t>
+  </si>
+  <si>
+    <t>0.0529,0.0029,0.9647,0.0066</t>
+  </si>
+  <si>
+    <t>0.6280,0.0462,0.2635,0.0619</t>
+  </si>
+  <si>
+    <t>0.0206,0.0045,0.9760,0.0105</t>
+  </si>
+  <si>
+    <t>0.0075,0.9814,0.0022,0.0034</t>
+  </si>
+  <si>
+    <t>0.0390,0.9420,0.0095,0.0045</t>
+  </si>
+  <si>
+    <t>0.0936,0.9250,0.0016,0.0035</t>
+  </si>
+  <si>
+    <t>0.1898,0.8560,0.0104,0.0030</t>
+  </si>
+  <si>
+    <t>0.0748,0.9265,0.0113,0.0023</t>
+  </si>
+  <si>
+    <t>0.0071,0.9816,0.0034,0.0029</t>
+  </si>
+  <si>
+    <t>0.4684,0.6633,0.0132,0.0008</t>
+  </si>
+  <si>
+    <t>0.5877,0.0926,0.3777,0.0325</t>
+  </si>
+  <si>
+    <t>0.2157,0.0058,0.8998,0.0101</t>
+  </si>
+  <si>
+    <t>0.3382,0.2859,0.1372,0.3065</t>
+  </si>
+  <si>
+    <t>0.5301,0.0583,0.3961,0.0868</t>
+  </si>
+  <si>
+    <t>0.1113,0.0849,0.0423,0.8897</t>
+  </si>
+  <si>
+    <t>0.0009,0.9938,0.0362,0.0010</t>
+  </si>
+  <si>
+    <t>0.0013,0.9909,0.0291,0.0033</t>
+  </si>
+  <si>
+    <t>0.0070,0.9474,0.0066,0.1661</t>
+  </si>
+  <si>
+    <t>0.0000,0.9402,0.9839,0.0000</t>
+  </si>
+  <si>
+    <t>0.0088,0.9846,0.0427,0.0003</t>
+  </si>
+  <si>
+    <t>0.8490,0.1054,0.0875,0.0031</t>
+  </si>
+  <si>
+    <t>0.9145,0.1206,0.0139,0.0015</t>
+  </si>
+  <si>
+    <t>0.9880,0.0078,0.0005,0.0016</t>
+  </si>
+  <si>
+    <t>0.9881,0.0013,0.0006,0.0058</t>
+  </si>
+  <si>
+    <t>0.9164,0.0811,0.0093,0.0076</t>
+  </si>
+  <si>
+    <t>0.9871,0.0078,0.0018,0.0012</t>
+  </si>
+  <si>
+    <t>0.9970,0.0003,0.0001,0.0014</t>
+  </si>
+  <si>
+    <t>0.9838,0.0056,0.0033,0.0024</t>
+  </si>
+  <si>
+    <t>0.9924,0.0017,0.0006,0.0021</t>
+  </si>
+  <si>
+    <t>0.9883,0.0054,0.0024,0.0012</t>
+  </si>
+  <si>
+    <t>0.0009,0.5474,0.9855,0.0002</t>
+  </si>
+  <si>
+    <t>0.0197,0.3850,0.8659,0.0012</t>
+  </si>
+  <si>
+    <t>0.0072,0.0646,0.9762,0.0003</t>
+  </si>
+  <si>
+    <t>0.0035,0.0295,0.9907,0.0002</t>
+  </si>
+  <si>
+    <t>0.8132,0.0290,0.0641,0.0415</t>
+  </si>
+  <si>
+    <t>0.8757,0.0243,0.0782,0.0074</t>
+  </si>
+  <si>
+    <t>0.2241,0.0028,0.9045,0.0090</t>
+  </si>
+  <si>
+    <t>0.6604,0.0331,0.3070,0.0325</t>
+  </si>
+  <si>
+    <t>0.0111,0.0004,0.0011,0.9947</t>
+  </si>
+  <si>
+    <t>0.0010,0.0003,0.0011,0.9987</t>
+  </si>
+  <si>
+    <t>0.0068,0.0071,0.0014,0.9949</t>
+  </si>
+  <si>
+    <t>0.0051,0.0001,0.0004,0.9979</t>
+  </si>
+  <si>
+    <t>0.0004,0.8077,0.9365,0.0006</t>
+  </si>
+  <si>
+    <t>0.9779,0.0093,0.0082,0.0015</t>
+  </si>
+  <si>
+    <t>0.7386,0.4030,0.0058,0.0020</t>
+  </si>
+  <si>
+    <t>0.9897,0.0011,0.0004,0.0050</t>
+  </si>
+  <si>
+    <t>0.6845,0.5703,0.0006,0.0005</t>
+  </si>
+  <si>
+    <t>0.9844,0.0040,0.0029,0.0027</t>
+  </si>
+  <si>
+    <t>0.8492,0.0259,0.0234,0.0900</t>
+  </si>
+  <si>
+    <t>0.9747,0.0140,0.0023,0.0039</t>
+  </si>
+  <si>
+    <t>0.0000,0.0843,0.9911,0.0031</t>
+  </si>
+  <si>
+    <t>0.8690,0.0053,0.0471,0.0487</t>
+  </si>
+  <si>
+    <t>0.9753,0.0065,0.0072,0.0033</t>
+  </si>
+  <si>
+    <t>0.8159,0.1518,0.0616,0.0024</t>
+  </si>
+  <si>
+    <t>0.8379,0.1098,0.0678,0.0033</t>
+  </si>
+  <si>
+    <t>0.9460,0.0261,0.0189,0.0022</t>
+  </si>
+  <si>
+    <t>0.1747,0.7014,0.0102,0.1169</t>
+  </si>
+  <si>
+    <t>0.8866,0.0824,0.0276,0.0025</t>
+  </si>
+  <si>
+    <t>0.9071,0.0950,0.0145,0.0019</t>
+  </si>
+  <si>
+    <t>0.9822,0.0098,0.0057,0.0013</t>
+  </si>
+  <si>
+    <t>0.9896,0.0057,0.0009,0.0017</t>
+  </si>
+  <si>
+    <t>0.9822,0.0035,0.0012,0.0084</t>
+  </si>
+  <si>
+    <t>0.9797,0.0016,0.0012,0.0201</t>
+  </si>
+  <si>
+    <t>0.9785,0.0101,0.0001,0.0024</t>
+  </si>
+  <si>
+    <t>0.9840,0.0051,0.0032,0.0025</t>
+  </si>
+  <si>
+    <t>0.9874,0.0082,0.0008,0.0012</t>
+  </si>
+  <si>
+    <t>0.9907,0.0020,0.0002,0.0033</t>
+  </si>
+  <si>
+    <t>0.5334,0.6427,0.0086,0.0008</t>
+  </si>
+  <si>
+    <t>0.7275,0.4135,0.0107,0.0009</t>
+  </si>
+  <si>
+    <t>0.3637,0.7750,0.0059,0.0006</t>
+  </si>
+  <si>
+    <t>0.4106,0.5397,0.1135,0.0005</t>
+  </si>
+  <si>
+    <t>0.9705,0.0424,0.0010,0.0009</t>
+  </si>
+  <si>
+    <t>0.9519,0.0646,0.0126,0.0002</t>
+  </si>
+  <si>
+    <t>0.9777,0.0230,0.0059,0.0007</t>
+  </si>
+  <si>
+    <t>0.9688,0.0376,0.0013,0.0016</t>
+  </si>
+  <si>
+    <t>0.0021,0.0114,0.9962,0.0009</t>
+  </si>
+  <si>
+    <t>0.9695,0.0226,0.0105,0.0013</t>
+  </si>
+  <si>
+    <t>0.0025,0.0027,0.9952,0.0038</t>
+  </si>
+  <si>
+    <t>0.0012,0.0170,0.9959,0.0007</t>
+  </si>
+  <si>
+    <t>0.0025,0.0016,0.9972,0.0005</t>
+  </si>
+  <si>
+    <t>0.0003,0.0781,0.9971,0.0002</t>
+  </si>
+  <si>
+    <t>0.0104,0.0245,0.9821,0.0010</t>
+  </si>
+  <si>
+    <t>0.0044,0.0059,0.9944,0.0003</t>
+  </si>
+  <si>
+    <t>0.0069,0.0043,0.9916,0.0027</t>
+  </si>
+  <si>
+    <t>0.2186,0.1731,0.6606,0.0224</t>
+  </si>
+  <si>
+    <t>0.3080,0.0063,0.8331,0.0056</t>
+  </si>
+  <si>
+    <t>0.3256,0.1021,0.6622,0.0063</t>
+  </si>
+  <si>
+    <t>0.4991,0.0495,0.6263,0.0021</t>
+  </si>
+  <si>
+    <t>0.1699,0.7168,0.1381,0.0273</t>
+  </si>
+  <si>
+    <t>0.6305,0.0579,0.4315,0.0061</t>
+  </si>
+  <si>
+    <t>0.2890,0.0355,0.7242,0.0850</t>
+  </si>
+  <si>
+    <t>0.5639,0.1558,0.3282,0.0230</t>
+  </si>
+  <si>
+    <t>0.9877,0.0244,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.6379,0.6400,0.0011,0.0002</t>
+  </si>
+  <si>
+    <t>0.9765,0.0325,0.0015,0.0008</t>
+  </si>
+  <si>
+    <t>0.9802,0.0368,0.0019,0.0002</t>
+  </si>
+  <si>
+    <t>0.9305,0.0963,0.0031,0.0025</t>
+  </si>
+  <si>
+    <t>0.5627,0.1924,0.2933,0.0318</t>
+  </si>
+  <si>
+    <t>0.4824,0.0376,0.6075,0.0306</t>
+  </si>
+  <si>
+    <t>0.5686,0.0609,0.1785,0.1815</t>
+  </si>
+  <si>
+    <t>0.5047,0.1241,0.2475,0.2275</t>
+  </si>
+  <si>
+    <t>0.5983,0.0275,0.2940,0.0719</t>
+  </si>
+  <si>
+    <t>0.1040,0.0416,0.8422,0.1039</t>
+  </si>
+  <si>
+    <t>0.0229,0.0870,0.9018,0.0290</t>
+  </si>
+  <si>
+    <t>0.0633,0.0475,0.8883,0.0198</t>
+  </si>
+  <si>
+    <t>0.0284,0.0079,0.9592,0.0127</t>
+  </si>
+  <si>
+    <t>0.0677,0.2321,0.7141,0.0035</t>
+  </si>
+  <si>
+    <t>0.9938,0.0051,0.0003,0.0005</t>
+  </si>
+  <si>
+    <t>0.9862,0.0137,0.0008,0.0009</t>
+  </si>
+  <si>
+    <t>0.9910,0.0050,0.0002,0.0011</t>
+  </si>
+  <si>
+    <t>0.9666,0.0582,0.0009,0.0009</t>
+  </si>
+  <si>
+    <t>0.9917,0.0067,0.0003,0.0008</t>
+  </si>
+  <si>
+    <t>0.9912,0.0116,0.0009,0.0001</t>
+  </si>
+  <si>
+    <t>0.9831,0.0217,0.0019,0.0007</t>
+  </si>
+  <si>
+    <t>0.9939,0.0031,0.0006,0.0007</t>
+  </si>
+  <si>
+    <t>0.1143,0.0072,0.9615,0.0007</t>
+  </si>
+  <si>
+    <t>0.6108,0.0466,0.5535,0.0041</t>
+  </si>
+  <si>
+    <t>0.8224,0.0093,0.1410,0.0262</t>
+  </si>
+  <si>
+    <t>0.0026,0.0054,0.9954,0.0013</t>
+  </si>
+  <si>
+    <t>0.0002,0.0314,0.9968,0.0005</t>
+  </si>
+  <si>
+    <t>0.0534,0.0352,0.9280,0.0060</t>
+  </si>
+  <si>
+    <t>0.0037,0.0018,0.9940,0.0011</t>
+  </si>
+  <si>
+    <t>0.1925,0.0257,0.8515,0.0032</t>
+  </si>
+  <si>
+    <t>0.0017,0.0237,0.9893,0.0041</t>
+  </si>
+  <si>
+    <t>0.0015,0.0078,0.9928,0.0034</t>
+  </si>
+  <si>
+    <t>0.1287,0.0706,0.8401,0.0117</t>
+  </si>
+  <si>
+    <t>0.1428,0.0009,0.4511,0.3660</t>
+  </si>
+  <si>
+    <t>0.0681,0.0054,0.9561,0.0110</t>
+  </si>
+  <si>
+    <t>0.7541,0.0275,0.1303,0.0480</t>
+  </si>
+  <si>
+    <t>0.9929,0.0016,0.0000,0.0016</t>
+  </si>
+  <si>
+    <t>0.9913,0.0063,0.0004,0.0008</t>
+  </si>
+  <si>
+    <t>0.9889,0.0089,0.0010,0.0008</t>
+  </si>
+  <si>
+    <t>0.9787,0.0260,0.0013,0.0011</t>
+  </si>
+  <si>
+    <t>0.9931,0.0048,0.0006,0.0006</t>
+  </si>
+  <si>
+    <t>0.9939,0.0042,0.0007,0.0004</t>
+  </si>
+  <si>
+    <t>0.9922,0.0028,0.0016,0.0007</t>
+  </si>
+  <si>
+    <t>0.9925,0.0073,0.0010,0.0002</t>
+  </si>
+  <si>
+    <t>0.0029,0.0837,0.9838,0.0004</t>
+  </si>
+  <si>
+    <t>0.0012,0.1365,0.9880,0.0010</t>
+  </si>
+  <si>
+    <t>0.0020,0.0337,0.9911,0.0006</t>
+  </si>
+  <si>
+    <t>0.0196,0.0119,0.9723,0.0020</t>
+  </si>
+  <si>
+    <t>0.0044,0.0048,0.9870,0.0057</t>
+  </si>
+  <si>
+    <t>0.2293,0.0465,0.7451,0.0743</t>
+  </si>
+  <si>
+    <t>0.1527,0.0261,0.8694,0.0053</t>
+  </si>
+  <si>
+    <t>0.0299,0.0233,0.8611,0.0957</t>
+  </si>
+  <si>
+    <t>0.5637,0.0054,0.0280,0.4880</t>
+  </si>
+  <si>
+    <t>0.0648,0.0116,0.0049,0.9702</t>
+  </si>
+  <si>
+    <t>0.0117,0.0021,0.0083,0.9895</t>
+  </si>
+  <si>
+    <t>0.0007,0.0003,0.0142,0.9962</t>
+  </si>
+  <si>
+    <t>0.0055,0.0001,0.0005,0.9973</t>
+  </si>
+  <si>
+    <t>0.4918,0.0299,0.5074,0.0804</t>
   </si>
 </sst>
 </file>
@@ -1959,7 +1965,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1973,7 +1979,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1984,10 +1990,10 @@
         <v>259</v>
       </c>
       <c r="C4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2001,7 +2007,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2015,7 +2021,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2029,7 +2035,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2043,7 +2049,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2057,7 +2063,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2071,7 +2077,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2085,7 +2091,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2099,7 +2105,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2113,7 +2119,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2127,7 +2133,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2141,7 +2147,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2155,7 +2161,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2169,7 +2175,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2183,7 +2189,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2197,7 +2203,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2211,7 +2217,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2225,7 +2231,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2239,7 +2245,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2253,7 +2259,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2264,10 +2270,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D24" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2281,7 +2287,7 @@
         <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2295,7 +2301,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2309,7 +2315,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2323,7 +2329,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2337,7 +2343,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2351,7 +2357,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2365,7 +2371,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2379,7 +2385,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2393,7 +2399,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2404,10 +2410,10 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2421,7 +2427,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2435,7 +2441,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2446,10 +2452,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2463,7 +2469,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2477,7 +2483,7 @@
         <v>261</v>
       </c>
       <c r="D39" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2491,7 +2497,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2505,7 +2511,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2519,7 +2525,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2533,7 +2539,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2547,7 +2553,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2561,7 +2567,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2572,10 +2578,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D46" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2589,7 +2595,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2603,7 +2609,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2617,7 +2623,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2631,7 +2637,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2645,7 +2651,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2659,7 +2665,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2673,7 +2679,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2687,7 +2693,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2701,7 +2707,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2715,7 +2721,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2729,7 +2735,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2743,7 +2749,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2757,7 +2763,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2771,7 +2777,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2785,7 +2791,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2799,7 +2805,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2813,7 +2819,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2827,7 +2833,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2841,7 +2847,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2855,7 +2861,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2869,7 +2875,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2883,7 +2889,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2897,7 +2903,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2911,7 +2917,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2925,7 +2931,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2939,7 +2945,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2953,7 +2959,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2967,7 +2973,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2978,10 +2984,10 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D75" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2992,10 +2998,10 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D76" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3009,7 +3015,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3023,7 +3029,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3037,7 +3043,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3051,7 +3057,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3065,7 +3071,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3079,7 +3085,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3093,7 +3099,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3104,10 +3110,10 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D84" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3118,10 +3124,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D85" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3135,7 +3141,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3149,7 +3155,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3160,10 +3166,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3177,7 +3183,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3191,7 +3197,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3205,7 +3211,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3219,7 +3225,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3233,7 +3239,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3247,7 +3253,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3261,7 +3267,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3275,7 +3281,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3289,7 +3295,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3303,7 +3309,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3317,7 +3323,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3331,7 +3337,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3345,7 +3351,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3359,7 +3365,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3373,7 +3379,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3387,7 +3393,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3401,7 +3407,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3415,7 +3421,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3426,10 +3432,10 @@
         <v>259</v>
       </c>
       <c r="C107" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3443,7 +3449,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3457,7 +3463,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3471,7 +3477,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3485,7 +3491,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3499,7 +3505,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3513,7 +3519,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3527,7 +3533,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3541,7 +3547,7 @@
         <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3555,7 +3561,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3569,7 +3575,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3580,10 +3586,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D118" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3597,7 +3603,7 @@
         <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3611,7 +3617,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3625,7 +3631,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3639,7 +3645,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3653,7 +3659,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3667,7 +3673,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3681,7 +3687,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3695,7 +3701,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3709,7 +3715,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3723,7 +3729,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3737,7 +3743,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3751,7 +3757,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3765,7 +3771,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3779,7 +3785,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3793,7 +3799,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3807,7 +3813,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3821,7 +3827,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3832,10 +3838,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3849,7 +3855,7 @@
         <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3863,7 +3869,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3877,7 +3883,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3891,7 +3897,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3905,7 +3911,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3919,7 +3925,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3933,7 +3939,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3947,7 +3953,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3961,7 +3967,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3975,7 +3981,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3989,7 +3995,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4003,7 +4009,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4017,7 +4023,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4028,10 +4034,10 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D150" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4045,7 +4051,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4056,10 +4062,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D152" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4073,7 +4079,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4087,7 +4093,7 @@
         <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4101,7 +4107,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4115,7 +4121,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4129,7 +4135,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4143,7 +4149,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4154,10 +4160,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4171,7 +4177,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4185,7 +4191,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4196,10 +4202,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4213,7 +4219,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4227,7 +4233,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4241,7 +4247,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4255,7 +4261,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4269,7 +4275,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4283,7 +4289,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4297,7 +4303,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4311,7 +4317,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4325,7 +4331,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4339,7 +4345,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4350,10 +4356,10 @@
         <v>259</v>
       </c>
       <c r="C173" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D173" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4364,10 +4370,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4381,7 +4387,7 @@
         <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4392,10 +4398,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D176" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4409,7 +4415,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4423,7 +4429,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4437,7 +4443,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4451,7 +4457,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4465,7 +4471,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4479,7 +4485,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4493,7 +4499,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4507,7 +4513,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4521,7 +4527,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4535,7 +4541,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4549,7 +4555,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4563,7 +4569,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4577,7 +4583,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4588,10 +4594,10 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4605,7 +4611,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4616,10 +4622,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4630,10 +4636,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4647,7 +4653,7 @@
         <v>262</v>
       </c>
       <c r="D194" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4661,7 +4667,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4675,7 +4681,7 @@
         <v>261</v>
       </c>
       <c r="D196" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4686,10 +4692,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D197" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4703,7 +4709,7 @@
         <v>259</v>
       </c>
       <c r="D198" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4714,10 +4720,10 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D199" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4731,7 +4737,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4745,7 +4751,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4759,7 +4765,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4773,7 +4779,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4784,10 +4790,10 @@
         <v>259</v>
       </c>
       <c r="C204" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D204" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4801,7 +4807,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4815,7 +4821,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4826,10 +4832,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4843,7 +4849,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4857,7 +4863,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4871,7 +4877,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4885,7 +4891,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4899,7 +4905,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4913,7 +4919,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4927,7 +4933,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4941,7 +4947,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4955,7 +4961,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4969,7 +4975,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4983,7 +4989,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4997,7 +5003,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5011,7 +5017,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5025,7 +5031,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5036,10 +5042,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D222" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5053,7 +5059,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5067,7 +5073,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5081,7 +5087,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5095,7 +5101,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5109,7 +5115,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5123,7 +5129,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5137,7 +5143,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5151,7 +5157,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5165,7 +5171,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5176,10 +5182,10 @@
         <v>259</v>
       </c>
       <c r="C232" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D232" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5193,7 +5199,7 @@
         <v>261</v>
       </c>
       <c r="D233" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5207,7 +5213,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5221,7 +5227,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5235,7 +5241,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5249,7 +5255,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5263,7 +5269,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5277,7 +5283,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5291,7 +5297,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5305,7 +5311,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5319,7 +5325,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5333,7 +5339,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5347,7 +5353,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5361,7 +5367,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5375,7 +5381,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5389,7 +5395,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5403,7 +5409,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5417,7 +5423,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5431,7 +5437,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5442,10 +5448,10 @@
         <v>259</v>
       </c>
       <c r="C251" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5459,7 +5465,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5473,7 +5479,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5487,7 +5493,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5501,7 +5507,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5512,10 +5518,10 @@
         <v>259</v>
       </c>
       <c r="C256" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D256" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
   </sheetData>
